--- a/output/2026-09-02_22_Italia_Molise_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-02_22_Italia_Molise_Utensilerie_e_Macchine_Utensili.xlsx
@@ -494,10 +494,9 @@
           <t>0874 62009 / 393 9254409</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Forniture industriali, utensili manuali/elettrici/a batteria, macchine utensili, strumenti di misura, saldatura, vuototecnica. Distributore B2B coerente.</t>
+          <t>Forniture industriali, utensili manuali/elettrici/a batteria, macchine utensili, strumenti di misura, saldatura, vuototecnica. Distributore B2B coerente. [DUPLICATO — vedi anche: 2026-09-02_16_Italia_Molise_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -532,7 +531,6 @@
           <t>0874 493123 / 338 5236853</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Rivenditore/dealer ufficiale utensili e ferramenta (Freud, Ica, Omnia Koll, Jowat), distribuisce anche in IS e BN.</t>
@@ -570,7 +568,6 @@
           <t>0874 62204 / 334 1657797</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Distributore materiali edili e ferramenta/utensili.</t>
@@ -588,7 +585,6 @@
           <t>Switech</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Campobasso</t>
@@ -604,10 +600,9 @@
           <t>0874 817577</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Grossista forniture industriali (bulloneria Friulsider, saldatura Saf-Fro, abrasivi Tyrolit, compressori ABAC, DPI Cofra); fornitore di rivenditori.</t>
+          <t>Grossista forniture industriali (bulloneria Friulsider, saldatura Saf-Fro, abrasivi Tyrolit, compressori ABAC, DPI Cofra); fornitore di rivenditori. [DUPLICATO — vedi anche: 2026-09-02_21_Italia_Molise_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -649,7 +644,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nonostante il nome, distributore di forniture agricole/industriali (motori, idropulitrici, compressori, bulloneria, cuscinetti, cinghie), non officina di lavorazione conto terzi.</t>
+          <t>Nonostante il nome, distributore di forniture agricole/industriali (motori, idropulitrici, compressori, bulloneria, cuscinetti, cinghie), non officina di lavorazione conto terzi. [DUPLICATO — vedi anche: 2026-09-02_15_Italia_Molise_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -691,7 +686,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Forniture industriali, utensileria, metallo duro, punte, fresatrici, utensili elettrici, macchine utensili, pneumatica.</t>
+          <t>Forniture industriali, utensileria, metallo duro, punte, fresatrici, utensili elettrici, macchine utensili, pneumatica. [DUPLICATO — vedi anche: 2026-09-02_18_Italia_Molise_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -726,7 +721,6 @@
           <t>0875 710120</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Punto vendita BigMat a Termoli (30.000 mq); reparto ferramenta/utensileria oltre a materiali edili.</t>
@@ -764,7 +758,6 @@
           <t>0875 471882 / 389 8465174</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Ferramenta/rivendita utensileria, viteria, vernici a Termoli dal 1991.</t>
@@ -782,7 +775,6 @@
           <t>Milano Ferramenta e C. Snc (Ferramenta Milano di Milano Valter &amp; C.)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Isernia</t>
@@ -862,7 +854,6 @@
           <t>Ferramenta E.G. di Peluso Emiliano e Rea Giuseppe Snc</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Isernia</t>
@@ -885,7 +876,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ferramenta/utensileria al dettaglio (P.IVA 00920360948).</t>
+          <t>Ferramenta/utensileria al dettaglio (P.IVA 00920360948). [DUPLICATO — vedi anche: 2026-09-02_21_Italia_Molise_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -900,7 +891,6 @@
           <t>Ferramenta Effedielle (Di Di Lullo Emilio &amp; Di Lullo Andrea Snc)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Isernia</t>
@@ -980,7 +970,6 @@
           <t>Ferramenta I.F.A. Srl</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Isernia</t>
@@ -996,7 +985,6 @@
           <t>0865 779212</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Ferramenta e utensileria ad Agnone, articoli DIY internazionali, servizio duplicazione chiavi.</t>
@@ -1014,7 +1002,6 @@
           <t>Ferramenta Cellilli Carmela</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Isernia</t>
@@ -1072,10 +1059,9 @@
           <t>0865 414346 / 351 7522429</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ATTENZIONE: attivita' principale termoidraulica; vende anche utensili/attrezzature professionali (Milwaukee, Hikoki) come linea secondaria - borderline, valutare priorita'.</t>
+          <t>ATTENZIONE: attivita' principale termoidraulica; vende anche utensili/attrezzature professionali (Milwaukee, Hikoki) come linea secondaria - borderline, valutare priorita'. [DUPLICATO — vedi anche: 2026-09-02_16_Italia_Molise_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
